--- a/pendaftaran_umum.xlsx
+++ b/pendaftaran_umum.xlsx
@@ -764,7 +764,7 @@
         <v>8123456789</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
@@ -826,9 +826,11 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAILED: Locator.click: Timeout 30000ms exceeded.
+          <t xml:space="preserve">FAILED: Locator.click: Error: strict mode violation: get_by_text("Konfirmasi Hadir", exact=True) resolved to 2 elements:
+    1) &lt;div class="tracking-wide"&gt;…&lt;/div&gt; aka get_by_role("button", name="Konfirmasi Hadir").first
+    2) &lt;div class="tracking-wide"&gt;…&lt;/div&gt; aka get_by_role("button", name="Konfirmasi Hadir").nth(1)
 Call log:
-  - waiting for locator("[id=\"Tanggal Pemeriksaan\"] .w-auto")
+  - waiting for get_by_text("Konfirmasi Hadir", exact=True)
 </t>
         </is>
       </c>
